--- a/results/Int All Data -0.2/Rando_6_permute.xlsx
+++ b/results/Int All Data -0.2/Rando_6_permute.xlsx
@@ -440,247 +440,247 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8148381274286634</v>
+        <v>0.8285852245292129</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8151370398473248</v>
+        <v>0.8316174610839024</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8157636062633649</v>
+        <v>0.8237710100940425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8163758018900462</v>
+        <v>0.8224891356832448</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8188676967648478</v>
+        <v>0.8218625692672047</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8188676967648478</v>
+        <v>0.8193850451817617</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8188245843967717</v>
+        <v>0.8109695109332966</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8442005242463958</v>
+        <v>0.8109695109332966</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8453386907636062</v>
+        <v>0.8106131153572003</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8563179738336668</v>
+        <v>0.8106131153572003</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8556626658389093</v>
+        <v>0.8106131153572003</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8576860729806166</v>
+        <v>0.809687636522499</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8585971810259594</v>
+        <v>0.8100009197305189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8613879883194224</v>
+        <v>0.8098026028373686</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8612586512151938</v>
+        <v>0.8088483824239499</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8587380147616748</v>
+        <v>0.8078510496424547</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8568583155135545</v>
+        <v>0.8090610701064589</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8666103331723805</v>
+        <v>0.80873341610908</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8563179738336668</v>
+        <v>0.8056724379756731</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8599336644363202</v>
+        <v>0.8056724379756731</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8837316916143569</v>
+        <v>0.8032955094157412</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8819066013657998</v>
+        <v>0.8014445517463383</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8808115472166655</v>
+        <v>0.8014445517463383</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8845651973971627</v>
+        <v>0.7946241751166908</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8812599158446575</v>
+        <v>0.7867920949161895</v>
       </c>
     </row>
     <row r="27">
@@ -690,1287 +690,1287 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.885378584074866</v>
+        <v>0.7758415534248466</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8736807615368697</v>
+        <v>0.7805120599664299</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8732122738037755</v>
+        <v>0.7740020923869306</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8760346968338277</v>
+        <v>0.7652732749304454</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8757357844151663</v>
+        <v>0.7524717757696995</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.871602745395599</v>
+        <v>0.7340311788645927</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.871602745395599</v>
+        <v>0.7264405279253179</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8658055689682922</v>
+        <v>0.7309270883631096</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8648800901335909</v>
+        <v>0.7278229978616265</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8676162884274907</v>
+        <v>0.7271964314455864</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8676306592168495</v>
+        <v>0.7447402910947092</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8699386079878595</v>
+        <v>0.7478731231749097</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.870864086822561</v>
+        <v>0.7469332735508496</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8658745487572141</v>
+        <v>0.7463067071348095</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8698351383044768</v>
+        <v>0.7469332735508496</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8695505966751742</v>
+        <v>0.7450535743027293</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8638511416155066</v>
+        <v>0.7568433698926215</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8626267503621439</v>
+        <v>0.7483703524867213</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8572118369317789</v>
+        <v>0.7507329102572946</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8542054677979352</v>
+        <v>0.7479564737531903</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8542054677979352</v>
+        <v>0.733174679818813</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.852213676392817</v>
+        <v>0.7410067600193143</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8555879377342439</v>
+        <v>0.7385004943551539</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8598215722793221</v>
+        <v>0.7419178680646571</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8598215722793221</v>
+        <v>0.7444816168862523</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8498769860430894</v>
+        <v>0.7556304752707457</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8225063806304753</v>
+        <v>0.7587058241935114</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8191177484996897</v>
+        <v>0.7551734841691384</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8087621576877975</v>
+        <v>0.7648996344071187</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7855705778206985</v>
+        <v>0.7729587730794878</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7682336575383413</v>
+        <v>0.7729731438688465</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7675783495435837</v>
+        <v>0.7658682256098963</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7751718746407302</v>
+        <v>0.7658682256098963</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7651439378262169</v>
+        <v>0.7658682256098963</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7722804718217562</v>
+        <v>0.7618673978524293</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7660263042928421</v>
+        <v>0.7625083350578281</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8084115104274447</v>
+        <v>0.7549751672759881</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8087391644248235</v>
+        <v>0.7609131774390103</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8023297923708353</v>
+        <v>0.75840691177485</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7934658894943781</v>
+        <v>0.7590622197696075</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8084776160584948</v>
+        <v>0.7593755029776276</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8042181140925708</v>
+        <v>0.776790025522522</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7936038490722218</v>
+        <v>0.7764767423145018</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7962107102618932</v>
+        <v>0.7749103262744016</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7968372766779334</v>
+        <v>0.7736140810742452</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7856682991883378</v>
+        <v>0.764784668092249</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7849555080361454</v>
+        <v>0.7620513439562209</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.831240946402704</v>
+        <v>0.7651841760364213</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8309132924053252</v>
+        <v>0.7511697822537997</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8251132418201467</v>
+        <v>0.7444183854130739</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8239607045135775</v>
+        <v>0.7433808144213745</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8225782345772689</v>
+        <v>0.7421564231680118</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8189884113954611</v>
+        <v>0.7445333517279438</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8277402221149204</v>
+        <v>0.7469677634453105</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8039077050424226</v>
+        <v>0.7469677634453105</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7957019843185946</v>
+        <v>0.7546992481203008</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7958169506334644</v>
+        <v>0.7558690303741005</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7792474305028627</v>
+        <v>0.7363736175300637</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7634596813133752</v>
+        <v>0.7363736175300637</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7634596813133752</v>
+        <v>0.7426249109011061</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7634596813133752</v>
+        <v>0.7420845692212181</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7508248833091904</v>
+        <v>0.7097215515853854</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7505116001011704</v>
+        <v>0.7069853532914856</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7505116001011704</v>
+        <v>0.7100032190568164</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7354998735370537</v>
+        <v>0.7091208525901911</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.736436849003242</v>
+        <v>0.6846014117863466</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6887488215952726</v>
+        <v>0.6717999126256007</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6979116368903912</v>
+        <v>0.6743492906578372</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6574578648456002</v>
+        <v>0.6892288059598537</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6194471269917914</v>
+        <v>0.6065708997263801</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6126669885723484</v>
+        <v>0.6129371594122922</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6319525878917477</v>
+        <v>0.612994642569727</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6316393046837276</v>
+        <v>0.6173806074820077</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6222954174426892</v>
+        <v>0.5622715044491964</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6047774252144121</v>
+        <v>0.5664706490998137</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6073555448253661</v>
+        <v>0.5658440826837736</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5794503460486078</v>
+        <v>0.5545515164056931</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5607137108827114</v>
+        <v>0.5615874548757214</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5584948610057253</v>
+        <v>0.5609177760916051</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5565001954427352</v>
+        <v>0.5625129337104229</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5632285990204871</v>
+        <v>0.5723368053160425</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5928065576786001</v>
+        <v>0.5814363891379826</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.593134211675979</v>
+        <v>0.5849112460049205</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5588368857924628</v>
+        <v>0.546762548573268</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5548935411924306</v>
+        <v>0.530655767860017</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5548935411924306</v>
+        <v>0.5214440918810789</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5573423236991562</v>
+        <v>0.5175840978593272</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5191303947943252</v>
+        <v>0.5237232990733716</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5198000735784415</v>
+        <v>0.5193085925823734</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5147990388816077</v>
+        <v>0.5262870478949667</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5132757352095836</v>
+        <v>0.5168598100756479</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5201478466809225</v>
+        <v>0.5200213837345657</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5201478466809225</v>
+        <v>0.5200213837345657</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5133964498401968</v>
+        <v>0.5156497896116438</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5351538249292958</v>
+        <v>0.5147099399875836</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5399220528385182</v>
+        <v>0.5165896392357039</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.518886091375227</v>
+        <v>0.5218435998252512</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5194839162125497</v>
+        <v>0.5190671633211469</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5194839162125497</v>
+        <v>0.5200357545239245</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4809558299418271</v>
+        <v>0.5187682509024856</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4809270883631096</v>
+        <v>0.5187682509024856</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4790473891149893</v>
+        <v>0.520119105102205</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4931106435814306</v>
+        <v>0.5229530247637443</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4819100503552459</v>
+        <v>0.5229530247637443</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4939067853119036</v>
+        <v>0.5263560276838886</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4845858913338392</v>
+        <v>0.5216855211423053</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4845858913338392</v>
+        <v>0.5188516014807661</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4825337426134143</v>
+        <v>0.513540157733784</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4855257409578994</v>
+        <v>0.513226874525764</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4858102825872019</v>
+        <v>0.5124738451633671</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4848704329631418</v>
+        <v>0.5124163620059323</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.503699041180934</v>
+        <v>0.5155491940861328</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.503699041180934</v>
+        <v>0.5145518613046377</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5028454162930261</v>
+        <v>0.5148938860913752</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5028454162930261</v>
+        <v>0.5135976408912188</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5084988848267458</v>
+        <v>0.5086569635096917</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5087977972454071</v>
+        <v>0.5092691591363731</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5082143431974432</v>
+        <v>0.5061938102136074</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4996723460026212</v>
+        <v>0.5061938102136074</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4996723460026212</v>
+        <v>0.50647835184291</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.5043428525442045</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4996723460026212</v>
+        <v>0.5085563679841807</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.5108470718079603</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.5020032880366053</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.4965078981858316</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.499315950426525</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.499315950426525</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.5002989124186613</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.5006265664160401</v>
       </c>
     </row>
     <row r="156">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
   </sheetData>
